--- a/data/trans_camb/P16A12-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,29</t>
+          <t>-2,01; 3,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,63</t>
+          <t>0,73; 6,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,08</t>
+          <t>0,46; 5,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,72</t>
+          <t>-0,37; 4,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,6</t>
+          <t>1,1; 6,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,62</t>
+          <t>2,22; 6,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,27</t>
+          <t>-0,58; 3,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,67</t>
+          <t>1,76; 5,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,54</t>
+          <t>2,3; 5,71</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 66,17</t>
+          <t>-27,69; 63,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 130,68</t>
+          <t>9,13; 127,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,77; 119,48</t>
+          <t>5,79; 118,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 119,73</t>
+          <t>-6,61; 132,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 162,14</t>
+          <t>11,76; 174,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,3; 181,05</t>
+          <t>35,92; 173,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 67,79</t>
+          <t>-9,29; 64,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,31; 116,9</t>
+          <t>26,01; 116,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,15; 122,65</t>
+          <t>34,79; 122,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,5</t>
+          <t>-1,97; 2,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,08</t>
+          <t>-0,63; 3,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,01</t>
+          <t>-3,51; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,88</t>
+          <t>-2,13; 2,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,39</t>
+          <t>-2,22; 2,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,06</t>
+          <t>-2,11; 2,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,14</t>
+          <t>-1,51; 1,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,57</t>
+          <t>-0,76; 2,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,71</t>
+          <t>-2,57; 1,79</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 50,79</t>
+          <t>-26,86; 49,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 79,52</t>
+          <t>-8,91; 72,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 55,01</t>
+          <t>-49,2; 51,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 45,4</t>
+          <t>-23,16; 43,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 37,99</t>
+          <t>-26,73; 39,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 34,56</t>
+          <t>-23,49; 34,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 34,81</t>
+          <t>-19,27; 32,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 42,29</t>
+          <t>-9,83; 42,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 25,93</t>
+          <t>-34,58; 27,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,17</t>
+          <t>-0,65; 4,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,17</t>
+          <t>1,86; 7,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,83</t>
+          <t>1,02; 5,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,34</t>
+          <t>-0,51; 5,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,58</t>
+          <t>-1,01; 4,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,1</t>
+          <t>-4,76; 0,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,94</t>
+          <t>0,32; 3,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,06</t>
+          <t>1,27; 5,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,53</t>
+          <t>-1,76; 2,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 123,29</t>
+          <t>-11,19; 126,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,85; 205,39</t>
+          <t>32,37; 213,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,14; 162,23</t>
+          <t>17,01; 173,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 115,6</t>
+          <t>-7,16; 107,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 97,31</t>
+          <t>-15,1; 95,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 20,11</t>
+          <t>-62,4; 17,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 86,91</t>
+          <t>4,93; 88,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,6; 111,67</t>
+          <t>20,16; 117,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,16; 54,0</t>
+          <t>-28,39; 57,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,79</t>
+          <t>1,47; 6,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,17</t>
+          <t>-0,1; 4,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,09</t>
+          <t>2,1; 6,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,73</t>
+          <t>2,14; 6,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,23</t>
+          <t>-0,05; 4,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,14</t>
+          <t>-0,76; 3,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,69</t>
+          <t>2,51; 5,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,76</t>
+          <t>0,61; 3,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,07</t>
+          <t>0,93; 3,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,28; 159,01</t>
+          <t>23,83; 148,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 94,49</t>
+          <t>-3,11; 91,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,12; 142,41</t>
+          <t>32,34; 148,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28,35; 146,4</t>
+          <t>32,19; 153,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 94,25</t>
+          <t>-2,27; 86,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 68,9</t>
+          <t>-11,17; 67,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,08; 120,47</t>
+          <t>40,48; 123,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,61; 78,19</t>
+          <t>10,22; 76,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,17; 86,75</t>
+          <t>15,36; 84,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,9</t>
+          <t>0,52; 2,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,99</t>
+          <t>1,56; 4,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,9</t>
+          <t>0,61; 3,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,71</t>
+          <t>1,17; 3,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,96</t>
+          <t>0,56; 3,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,9</t>
+          <t>-0,46; 1,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,96</t>
+          <t>1,19; 2,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,17</t>
+          <t>1,31; 3,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,69</t>
+          <t>0,56; 2,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,13; 56,54</t>
+          <t>9,37; 59,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24,88; 78,04</t>
+          <t>23,78; 77,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,5; 75,76</t>
+          <t>10,52; 74,64</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,73; 65,63</t>
+          <t>17,62; 68,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,44; 53,84</t>
+          <t>8,55; 55,36</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 33,87</t>
+          <t>-6,91; 35,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,82; 53,44</t>
+          <t>19,2; 53,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>22,72; 58,32</t>
+          <t>21,18; 57,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9,74; 48,69</t>
+          <t>9,32; 47,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A12-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>3,72</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,3</t>
+          <t>-2,05; 3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,29</t>
+          <t>0,49; 6,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,91</t>
+          <t>0,54; 6,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,81</t>
+          <t>-0,4; 4,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,89</t>
+          <t>0,93; 6,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,39</t>
+          <t>1,83; 6,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,19</t>
+          <t>-0,49; 3,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,58</t>
+          <t>1,43; 5,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,71</t>
+          <t>2,11; 5,43</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 63,88</t>
+          <t>-28,71; 67,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 127,6</t>
+          <t>5,64; 123,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 118,12</t>
+          <t>5,95; 118,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 132,99</t>
+          <t>-9,6; 118,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 174,01</t>
+          <t>12,42; 169,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,92; 173,08</t>
+          <t>27,49; 174,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 64,98</t>
+          <t>-7,88; 69,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,01; 116,54</t>
+          <t>22,61; 115,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,79; 122,78</t>
+          <t>32,08; 114,03</t>
         </is>
       </c>
     </row>
@@ -850,29 +850,29 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,46</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,86</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,53</t>
+          <t>-1,81; 2,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,82</t>
+          <t>-0,5; 4,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 2,86</t>
+          <t>-0,15; 4,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,75</t>
+          <t>-2,03; 2,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,56</t>
+          <t>-2,59; 2,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,11</t>
+          <t>-2,22; 2,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,93</t>
+          <t>-1,34; 2,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,48</t>
+          <t>-0,76; 2,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,79</t>
+          <t>-0,45; 2,66</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 49,48</t>
+          <t>-25,45; 51,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 72,6</t>
+          <t>-6,76; 85,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 51,99</t>
+          <t>-2,02; 85,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 43,12</t>
+          <t>-23,19; 49,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 39,75</t>
+          <t>-28,83; 38,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 34,5</t>
+          <t>-24,03; 32,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 32,45</t>
+          <t>-17,31; 35,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 42,39</t>
+          <t>-10,27; 43,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 27,96</t>
+          <t>-5,55; 46,73</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>1,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,18</t>
+          <t>-0,36; 4,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,37</t>
+          <t>2,28; 7,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,88</t>
+          <t>0,84; 5,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,04</t>
+          <t>-0,3; 5,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,62</t>
+          <t>-0,77; 4,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,94</t>
+          <t>-2,38; 2,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,97</t>
+          <t>0,59; 4,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,18</t>
+          <t>1,44; 5,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,61</t>
+          <t>-0,03; 3,22</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-22,82%</t>
+          <t>-1,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 126,73</t>
+          <t>-9,83; 128,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,37; 213,91</t>
+          <t>39,41; 205,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,01; 173,73</t>
+          <t>12,07; 155,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 107,71</t>
+          <t>-4,39; 111,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 95,88</t>
+          <t>-12,98; 88,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,4; 17,02</t>
+          <t>-32,67; 44,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,93; 88,93</t>
+          <t>7,58; 88,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,16; 117,67</t>
+          <t>22,51; 116,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 57,81</t>
+          <t>-0,52; 71,36</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>2,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,46</t>
+          <t>1,75; 6,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 4,08</t>
+          <t>0,09; 4,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,63</t>
+          <t>1,79; 5,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,97</t>
+          <t>2,0; 6,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,22</t>
+          <t>0,1; 4,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,11</t>
+          <t>-0,11; 3,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,92</t>
+          <t>2,55; 5,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,63</t>
+          <t>0,52; 3,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,98</t>
+          <t>1,44; 4,24</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>52,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,83; 148,22</t>
+          <t>30,09; 145,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 91,45</t>
+          <t>1,52; 92,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,34; 148,33</t>
+          <t>28,83; 138,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32,19; 153,59</t>
+          <t>28,87; 155,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 86,43</t>
+          <t>-1,75; 95,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 67,8</t>
+          <t>-1,89; 82,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,48; 123,16</t>
+          <t>40,96; 122,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,22; 76,22</t>
+          <t>8,35; 72,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,36; 84,91</t>
+          <t>22,95; 91,82</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>2,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,91</t>
+          <t>0,44; 2,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,02</t>
+          <t>1,48; 3,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,76</t>
+          <t>1,86; 4,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,68</t>
+          <t>1,2; 3,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,08</t>
+          <t>0,53; 3,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,98</t>
+          <t>0,25; 2,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,92</t>
+          <t>1,21; 2,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,14</t>
+          <t>1,42; 3,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,57</t>
+          <t>1,43; 2,99</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,37; 59,52</t>
+          <t>6,85; 56,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>23,78; 77,83</t>
+          <t>23,48; 77,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10,52; 74,64</t>
+          <t>30,14; 82,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,62; 68,76</t>
+          <t>17,89; 66,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,55; 55,36</t>
+          <t>7,87; 56,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 35,7</t>
+          <t>3,46; 41,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,2; 53,92</t>
+          <t>19,11; 53,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21,18; 57,99</t>
+          <t>22,47; 57,97</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9,32; 47,17</t>
+          <t>22,88; 56,3</t>
         </is>
       </c>
     </row>
